--- a/config/yunying/dispatch_task.xlsx
+++ b/config/yunying/dispatch_task.xlsx
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>本日ログイン</t>
+          <t>今日登录</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>任意の仲間を10回レベルアップ</t>
+          <t>任意伙伴升级10次</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>アリーナで合計5回戦闘</t>
+          <t>在竞技场总共战斗5次</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>精鋭ステージに10回挑戦</t>
+          <t>挑战10次精锐关卡</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5回回収</t>
+          <t>回收5次</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>累計200ダイヤを消費</t>
+          <t>累计消费200颗钻石</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
